--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2021_atacama.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:22</t>
+    <t xml:space="preserve">2026-09-24 01:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>0.21</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.72</v>
@@ -762,7 +762,7 @@
         <v>0.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.18</v>
@@ -785,7 +785,7 @@
         <v>0.14</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.72</v>
@@ -805,13 +805,13 @@
         <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="14">
